--- a/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T12:54:23+00:00</t>
+    <t>2024-02-07T14:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T14:54:44+00:00</t>
+    <t>2024-02-09T10:35:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T10:35:57+00:00</t>
+    <t>2024-02-09T17:32:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T17:32:50+00:00</t>
+    <t>2024-02-12T09:02:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T09:02:55+00:00</t>
+    <t>2024-02-12T10:14:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T10:14:03+00:00</t>
+    <t>2024-02-12T13:01:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/maj-spec-contenu-CISIS/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T13:01:41+00:00</t>
+    <t>2024-02-12T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
